--- a/numerical-workflows/v2/framework/05_验算核算/十四日活动CHG012_20260831/SVN落表-20260903/TaskTarget-before-06.xlsx
+++ b/numerical-workflows/v2/framework/05_验算核算/十四日活动CHG012_20260831/SVN落表-20260903/TaskTarget-before-06.xlsx
@@ -8132,7 +8132,9 @@
       <c r="H246" s="54" t="n">
         <v>0</v>
       </c>
-      <c r="I246" s="54" t="n"/>
+      <c r="I246" s="54" t="n">
+        <v>17</v>
+      </c>
       <c r="J246" s="54" t="n"/>
       <c r="K246" s="54" t="n"/>
     </row>
@@ -8219,7 +8221,9 @@
       <c r="H249" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="I249" s="0" t="n"/>
+      <c r="I249" s="0" t="n">
+        <v>204</v>
+      </c>
       <c r="J249" s="0" t="n"/>
     </row>
     <row r="250" ht="21" customHeight="1" s="1">
@@ -8481,7 +8485,9 @@
       <c r="H258" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="I258" s="0" t="n"/>
+      <c r="I258" s="0" t="n">
+        <v>314</v>
+      </c>
       <c r="J258" s="0" t="inlineStr">
         <is>
           <t>复用旧类型，需联调确认按本周最高分统计</t>
@@ -8513,7 +8519,9 @@
       <c r="H259" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="I259" s="0" t="n"/>
+      <c r="I259" s="0" t="n">
+        <v>201</v>
+      </c>
       <c r="J259" s="0" t="n"/>
     </row>
     <row r="260" ht="21" customHeight="1" s="1">
@@ -8809,7 +8817,9 @@
       <c r="H269" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="I269" s="0" t="n"/>
+      <c r="I269" s="0" t="n">
+        <v>314</v>
+      </c>
       <c r="J269" s="0" t="n"/>
     </row>
     <row r="270">
@@ -9042,7 +9052,7 @@
         <v>0</v>
       </c>
       <c r="I277" s="0" t="n">
-        <v>26</v>
+        <v>213</v>
       </c>
       <c r="J277" s="0" t="n"/>
     </row>
@@ -9310,7 +9320,7 @@
         <v>0</v>
       </c>
       <c r="I286" s="0" t="n">
-        <v>26</v>
+        <v>204</v>
       </c>
       <c r="J286" s="0" t="n"/>
     </row>
@@ -9340,7 +9350,7 @@
         <v>0</v>
       </c>
       <c r="I287" s="0" t="n">
-        <v>26</v>
+        <v>213</v>
       </c>
       <c r="J287" s="0" t="n"/>
     </row>
@@ -9672,7 +9682,7 @@
         <v>0</v>
       </c>
       <c r="I298" s="0" t="n">
-        <v>26</v>
+        <v>213</v>
       </c>
       <c r="J298" s="0" t="n"/>
     </row>
@@ -9701,7 +9711,9 @@
       <c r="H299" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="I299" s="0" t="n"/>
+      <c r="I299" s="0" t="n">
+        <v>203</v>
+      </c>
       <c r="J299" s="0" t="n"/>
     </row>
     <row r="300">
@@ -9967,7 +9979,9 @@
       <c r="H308" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="I308" s="0" t="n"/>
+      <c r="I308" s="0" t="n">
+        <v>203</v>
+      </c>
       <c r="J308" s="0" t="n"/>
     </row>
     <row r="309">
@@ -10098,7 +10112,7 @@
         <v>0</v>
       </c>
       <c r="I313" s="0" t="n">
-        <v>26</v>
+        <v>213</v>
       </c>
     </row>
     <row r="314">
@@ -10251,7 +10265,7 @@
         <v>0</v>
       </c>
       <c r="I319" s="0" t="n">
-        <v>26</v>
+        <v>213</v>
       </c>
     </row>
     <row r="320">
@@ -10401,7 +10415,7 @@
         <v>0</v>
       </c>
       <c r="I325" s="0" t="n">
-        <v>26</v>
+        <v>213</v>
       </c>
     </row>
     <row r="326">
@@ -10554,7 +10568,7 @@
         <v>0</v>
       </c>
       <c r="I331" s="0" t="n">
-        <v>26</v>
+        <v>213</v>
       </c>
     </row>
     <row r="332">
@@ -10701,7 +10715,7 @@
         <v>0</v>
       </c>
       <c r="I337" s="0" t="n">
-        <v>26</v>
+        <v>213</v>
       </c>
     </row>
     <row r="338">
@@ -10854,7 +10868,7 @@
         <v>0</v>
       </c>
       <c r="I343" s="0" t="n">
-        <v>26</v>
+        <v>213</v>
       </c>
     </row>
     <row r="344">
@@ -11004,7 +11018,7 @@
         <v>0</v>
       </c>
       <c r="I349" s="0" t="n">
-        <v>26</v>
+        <v>213</v>
       </c>
     </row>
     <row r="350">
